--- a/KatalonData/IWPBootstrapDataDemo/VRelayPaymentsCC_25.xlsx
+++ b/KatalonData/IWPBootstrapDataDemo/VRelayPaymentsCC_25.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t476046\Documents\VPS-Katalon-feature-VRelay\KatalonData\IWPBootstrapDataDemo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49036B96-169E-4027-9B63-33933B0DBF51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{544D5830-5E07-451D-B658-D99D08CE6D3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2304" yWindow="1752" windowWidth="17280" windowHeight="9972" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2844" yWindow="2052" windowWidth="17280" windowHeight="9972" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PayNowCCNoCF" sheetId="1" r:id="rId1"/>
@@ -18,10 +18,11 @@
     <sheet name="PayNowCCDCF" sheetId="3" r:id="rId3"/>
     <sheet name="PayNowDCNoCF" sheetId="4" r:id="rId4"/>
     <sheet name="CMCAutopayCC" sheetId="9" r:id="rId5"/>
-    <sheet name="PayNowDCSCF" sheetId="5" r:id="rId6"/>
-    <sheet name="PayNowDCDCF" sheetId="6" r:id="rId7"/>
-    <sheet name="CCDeferredCC" sheetId="7" r:id="rId8"/>
-    <sheet name="CCDeferredDC" sheetId="8" r:id="rId9"/>
+    <sheet name="NoModifyAmountCC" sheetId="10" r:id="rId6"/>
+    <sheet name="PayNowDCSCF" sheetId="5" r:id="rId7"/>
+    <sheet name="PayNowDCDCF" sheetId="6" r:id="rId8"/>
+    <sheet name="CCDeferredCC" sheetId="7" r:id="rId9"/>
+    <sheet name="CCDeferredDC" sheetId="8" r:id="rId10"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="46">
   <si>
     <t>Result</t>
   </si>
@@ -156,6 +157,21 @@
   </si>
   <si>
     <t>36</t>
+  </si>
+  <si>
+    <t>Thu Jun 04 23:32:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Pay Now Credit Card, Emulator Data is overwritten</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>6425</t>
   </si>
 </sst>
 </file>
@@ -206,13 +222,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -585,6 +604,104 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE3BD9EF-09CF-47C3-B934-D79A532B2550}">
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62207C34-03C9-4772-84A8-17E8C44A63D7}">
   <dimension ref="A1:N2"/>
@@ -961,6 +1078,104 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{885C1BE4-A9C2-447B-960A-540E867D6683}">
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E9D48FF-3EB3-4130-A9CE-771D994AFBC3}">
   <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1054,7 +1269,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D59F2560-40CE-454F-A9CC-B5E3A656EC82}">
   <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1148,7 +1363,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40ABC5F0-6A33-43C4-B16C-62020B0254E6}">
   <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1245,102 +1460,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE3BD9EF-09CF-47C3-B934-D79A532B2550}">
-  <dimension ref="A1:N2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>